--- a/SUIM/TEST/evaluation_results.xlsx
+++ b/SUIM/TEST/evaluation_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emanu\Desktop\Mestrado\2A\1S\VCOM\Assignment_2\SUIM\TEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49546CF6-D2C1-43F5-8571-B5D20766EC31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEA2AD0E-59D1-4E67-8434-E77E00CF3C08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="F-Score" sheetId="1" r:id="rId1"/>
@@ -502,6 +502,7 @@
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="14.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="6" width="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
   </cols>

--- a/SUIM/TEST/evaluation_results.xlsx
+++ b/SUIM/TEST/evaluation_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emanu\Desktop\Mestrado\2A\1S\VCOM\Assignment_2\SUIM\TEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEA2AD0E-59D1-4E67-8434-E77E00CF3C08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2A30B44-984B-4B77-9ACD-9A7849F191DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="468" windowWidth="16500" windowHeight="12480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="F-Score" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="58">
   <si>
     <t>HD</t>
   </si>
@@ -62,6 +62,69 @@
     <t>87.14 ± 5.13</t>
   </si>
   <si>
+    <t>SUIM-Net_VGG_Noaug1_2</t>
+  </si>
+  <si>
+    <t>69.25 ± 25.82</t>
+  </si>
+  <si>
+    <t>42.71 ± 17.14</t>
+  </si>
+  <si>
+    <t>55.43 ± 25.09</t>
+  </si>
+  <si>
+    <t>42.64 ± 24.13</t>
+  </si>
+  <si>
+    <t>70.10 ± 22.24</t>
+  </si>
+  <si>
+    <t>56.03 ± 12.08</t>
+  </si>
+  <si>
+    <t>SUIM-Net_VGG_Noaug</t>
+  </si>
+  <si>
+    <t>72.33 ± 25.37</t>
+  </si>
+  <si>
+    <t>42.83 ± 20.63</t>
+  </si>
+  <si>
+    <t>54.31 ± 37.81</t>
+  </si>
+  <si>
+    <t>49.20 ± 24.08</t>
+  </si>
+  <si>
+    <t>69.07 ± 22.76</t>
+  </si>
+  <si>
+    <t>57.55 ± 11.38</t>
+  </si>
+  <si>
+    <t>SUIM-Net_VGG_Aug</t>
+  </si>
+  <si>
+    <t>64.21 ± 28.15</t>
+  </si>
+  <si>
+    <t>26.64 ± 13.18</t>
+  </si>
+  <si>
+    <t>49.10 ± 26.08</t>
+  </si>
+  <si>
+    <t>31.63 ± 20.78</t>
+  </si>
+  <si>
+    <t>56.77 ± 26.33</t>
+  </si>
+  <si>
+    <t>45.67 ± 14.41</t>
+  </si>
+  <si>
     <t>84.78 ± 16.83</t>
   </si>
   <si>
@@ -78,6 +141,60 @@
   </si>
   <si>
     <t>84.44 ± 5.21</t>
+  </si>
+  <si>
+    <t>61.37 ± 24.78</t>
+  </si>
+  <si>
+    <t>57.87 ± 24.79</t>
+  </si>
+  <si>
+    <t>54.29 ± 26.92</t>
+  </si>
+  <si>
+    <t>61.87 ± 27.06</t>
+  </si>
+  <si>
+    <t>62.93 ± 23.27</t>
+  </si>
+  <si>
+    <t>59.67 ± 3.18</t>
+  </si>
+  <si>
+    <t>66.10 ± 23.48</t>
+  </si>
+  <si>
+    <t>52.91 ± 27.56</t>
+  </si>
+  <si>
+    <t>52.48 ± 34.17</t>
+  </si>
+  <si>
+    <t>68.97 ± 24.48</t>
+  </si>
+  <si>
+    <t>61.86 ± 24.22</t>
+  </si>
+  <si>
+    <t>60.46 ± 6.74</t>
+  </si>
+  <si>
+    <t>60.31 ± 27.20</t>
+  </si>
+  <si>
+    <t>40.91 ± 24.06</t>
+  </si>
+  <si>
+    <t>48.37 ± 27.02</t>
+  </si>
+  <si>
+    <t>47.83 ± 31.17</t>
+  </si>
+  <si>
+    <t>53.62 ± 28.63</t>
+  </si>
+  <si>
+    <t>50.21 ± 6.47</t>
   </si>
 </sst>
 </file>
@@ -441,12 +558,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -490,6 +606,75 @@
       </c>
       <c r="G2" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -499,11 +684,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.88671875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -532,22 +716,91 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" t="s">
-        <v>18</v>
+      <c r="B3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G5" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/SUIM/TEST/evaluation_results.xlsx
+++ b/SUIM/TEST/evaluation_results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emanu\Desktop\Mestrado\2A\1S\VCOM\Assignment_2\SUIM\TEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2A30B44-984B-4B77-9ACD-9A7849F191DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34725720-2AEA-41BE-968E-8313D005064F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="468" windowWidth="16500" windowHeight="12480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="F-Score" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="71">
   <si>
     <t>HD</t>
   </si>
@@ -125,6 +125,27 @@
     <t>45.67 ± 14.41</t>
   </si>
   <si>
+    <t>SUIM-Net_SWIN_NOAUG</t>
+  </si>
+  <si>
+    <t>70.96 ± 29.04</t>
+  </si>
+  <si>
+    <t>52.61 ± 29.23</t>
+  </si>
+  <si>
+    <t>52.74 ± 30.21</t>
+  </si>
+  <si>
+    <t>51.35 ± 27.94</t>
+  </si>
+  <si>
+    <t>73.04 ± 22.77</t>
+  </si>
+  <si>
+    <t>60.14 ± 9.72</t>
+  </si>
+  <si>
     <t>84.78 ± 16.83</t>
   </si>
   <si>
@@ -195,6 +216,24 @@
   </si>
   <si>
     <t>50.21 ± 6.47</t>
+  </si>
+  <si>
+    <t>68.93 ± 28.89</t>
+  </si>
+  <si>
+    <t>65.43 ± 35.62</t>
+  </si>
+  <si>
+    <t>56.28 ± 31.02</t>
+  </si>
+  <si>
+    <t>72.05 ± 29.39</t>
+  </si>
+  <si>
+    <t>68.84 ± 25.17</t>
+  </si>
+  <si>
+    <t>66.31 ± 5.43</t>
   </si>
 </sst>
 </file>
@@ -213,7 +252,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -558,10 +596,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -675,6 +713,29 @@
       </c>
       <c r="G5" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -684,10 +745,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -716,22 +778,22 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="F2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -739,22 +801,22 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E3" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F3" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -762,22 +824,22 @@
         <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G4" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -785,22 +847,45 @@
         <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G5" t="s">
-        <v>57</v>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" t="s">
+        <v>68</v>
+      </c>
+      <c r="F6" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/SUIM/TEST/evaluation_results.xlsx
+++ b/SUIM/TEST/evaluation_results.xlsx
@@ -8,20 +8,33 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emanu\Desktop\Mestrado\2A\1S\VCOM\Assignment_2\SUIM\TEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34725720-2AEA-41BE-968E-8313D005064F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60333127-6B7F-40AE-897E-61BE7E4A2722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2580" yWindow="864" windowWidth="16500" windowHeight="12480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="F-Score" sheetId="1" r:id="rId1"/>
     <sheet name="mIoU" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="168">
   <si>
     <t>HD</t>
   </si>
@@ -41,6 +54,9 @@
     <t>Combined</t>
   </si>
   <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
     <t>SUIM-Net_VGG</t>
   </si>
   <si>
@@ -146,6 +162,159 @@
     <t>60.14 ± 9.72</t>
   </si>
   <si>
+    <t>SUIM-Net_SWIN_2</t>
+  </si>
+  <si>
+    <t>71.30 ± 28.72</t>
+  </si>
+  <si>
+    <t>55.98 ± 24.37</t>
+  </si>
+  <si>
+    <t>49.18 ± 36.74</t>
+  </si>
+  <si>
+    <t>49.69 ± 26.09</t>
+  </si>
+  <si>
+    <t>68.25 ± 26.12</t>
+  </si>
+  <si>
+    <t>58.88 ± 9.26</t>
+  </si>
+  <si>
+    <t>SUIM-Net_SWIN_AUG</t>
+  </si>
+  <si>
+    <t>63.01 ± 27.05</t>
+  </si>
+  <si>
+    <t>36.03 ± 27.26</t>
+  </si>
+  <si>
+    <t>26.78 ± 24.68</t>
+  </si>
+  <si>
+    <t>40.14 ± 26.25</t>
+  </si>
+  <si>
+    <t>58.53 ± 30.03</t>
+  </si>
+  <si>
+    <t>44.90 ± 13.74</t>
+  </si>
+  <si>
+    <t>SUIM-Net_SWIN_AUG_2</t>
+  </si>
+  <si>
+    <t>53.10 ± 29.13</t>
+  </si>
+  <si>
+    <t>40.98 ± 23.14</t>
+  </si>
+  <si>
+    <t>42.64 ± 29.64</t>
+  </si>
+  <si>
+    <t>40.24 ± 26.38</t>
+  </si>
+  <si>
+    <t>57.04 ± 29.35</t>
+  </si>
+  <si>
+    <t>46.80 ± 6.91</t>
+  </si>
+  <si>
+    <t>Epoch 46</t>
+  </si>
+  <si>
+    <t>SUIM-Net_SWIN_3</t>
+  </si>
+  <si>
+    <t>73.51 ± 26.59</t>
+  </si>
+  <si>
+    <t>55.54 ± 24.45</t>
+  </si>
+  <si>
+    <t>56.75 ± 34.75</t>
+  </si>
+  <si>
+    <t>47.67 ± 28.97</t>
+  </si>
+  <si>
+    <t>70.62 ± 25.76</t>
+  </si>
+  <si>
+    <t>60.82 ± 9.74</t>
+  </si>
+  <si>
+    <t>Epoch 72</t>
+  </si>
+  <si>
+    <t>SUIM-Net_RSB_KERAS</t>
+  </si>
+  <si>
+    <t>88.72 ± 13.57</t>
+  </si>
+  <si>
+    <t>57.02 ± 22.93</t>
+  </si>
+  <si>
+    <t>71.93 ± 24.60</t>
+  </si>
+  <si>
+    <t>70.06 ± 18.44</t>
+  </si>
+  <si>
+    <t>83.49 ± 15.76</t>
+  </si>
+  <si>
+    <t>74.24 ± 11.08</t>
+  </si>
+  <si>
+    <t>SUIM-Net_RSB_Aug</t>
+  </si>
+  <si>
+    <t>26.22 ± 23.90</t>
+  </si>
+  <si>
+    <t>7.75 ± 8.85</t>
+  </si>
+  <si>
+    <t>6.87 ± 13.58</t>
+  </si>
+  <si>
+    <t>27.26 ± 16.16</t>
+  </si>
+  <si>
+    <t>26.33 ± 21.77</t>
+  </si>
+  <si>
+    <t>18.89 ± 9.46</t>
+  </si>
+  <si>
+    <t>SUIM-Net_RSB_noAug</t>
+  </si>
+  <si>
+    <t>47.48 ± 25.04</t>
+  </si>
+  <si>
+    <t>22.20 ± 15.47</t>
+  </si>
+  <si>
+    <t>31.23 ± 22.57</t>
+  </si>
+  <si>
+    <t>30.20 ± 21.05</t>
+  </si>
+  <si>
+    <t>47.23 ± 25.03</t>
+  </si>
+  <si>
+    <t>35.67 ± 10.04</t>
+  </si>
+  <si>
     <t>84.78 ± 16.83</t>
   </si>
   <si>
@@ -164,6 +333,9 @@
     <t>84.44 ± 5.21</t>
   </si>
   <si>
+    <t>Paper</t>
+  </si>
+  <si>
     <t>61.37 ± 24.78</t>
   </si>
   <si>
@@ -234,6 +406,138 @@
   </si>
   <si>
     <t>66.31 ± 5.43</t>
+  </si>
+  <si>
+    <t>68.58 ± 28.72</t>
+  </si>
+  <si>
+    <t>68.87 ± 31.40</t>
+  </si>
+  <si>
+    <t>51.77 ± 36.94</t>
+  </si>
+  <si>
+    <t>71.65 ± 28.15</t>
+  </si>
+  <si>
+    <t>64.26 ± 27.52</t>
+  </si>
+  <si>
+    <t>65.03 ± 7.04</t>
+  </si>
+  <si>
+    <t>63.80 ± 29.11</t>
+  </si>
+  <si>
+    <t>54.40 ± 36.59</t>
+  </si>
+  <si>
+    <t>32.18 ± 31.14</t>
+  </si>
+  <si>
+    <t>65.02 ± 32.67</t>
+  </si>
+  <si>
+    <t>60.75 ± 29.85</t>
+  </si>
+  <si>
+    <t>55.23 ± 12.09</t>
+  </si>
+  <si>
+    <t>56.93 ± 32.39</t>
+  </si>
+  <si>
+    <t>63.46 ± 32.14</t>
+  </si>
+  <si>
+    <t>50.03 ± 31.70</t>
+  </si>
+  <si>
+    <t>65.43 ± 33.23</t>
+  </si>
+  <si>
+    <t>59.97 ± 30.23</t>
+  </si>
+  <si>
+    <t>59.16 ± 5.42</t>
+  </si>
+  <si>
+    <t>epoch 46</t>
+  </si>
+  <si>
+    <t>70.63 ± 26.40</t>
+  </si>
+  <si>
+    <t>66.47 ± 31.94</t>
+  </si>
+  <si>
+    <t>57.68 ± 35.06</t>
+  </si>
+  <si>
+    <t>70.29 ± 30.02</t>
+  </si>
+  <si>
+    <t>67.48 ± 26.83</t>
+  </si>
+  <si>
+    <t>66.51 ± 4.69</t>
+  </si>
+  <si>
+    <t>epoch 72</t>
+  </si>
+  <si>
+    <t>81.06 ± 17.66</t>
+  </si>
+  <si>
+    <t>77.30 ± 17.55</t>
+  </si>
+  <si>
+    <t>63.79 ± 22.48</t>
+  </si>
+  <si>
+    <t>84.39 ± 18.06</t>
+  </si>
+  <si>
+    <t>76.43 ± 20.21</t>
+  </si>
+  <si>
+    <t>76.59 ± 7.00</t>
+  </si>
+  <si>
+    <t>26.59 ± 26.85</t>
+  </si>
+  <si>
+    <t>12.92 ± 21.83</t>
+  </si>
+  <si>
+    <t>4.48 ± 7.56</t>
+  </si>
+  <si>
+    <t>54.22 ± 29.62</t>
+  </si>
+  <si>
+    <t>27.52 ± 25.96</t>
+  </si>
+  <si>
+    <t>25.15 ± 16.91</t>
+  </si>
+  <si>
+    <t>42.73 ± 26.44</t>
+  </si>
+  <si>
+    <t>24.10 ± 23.58</t>
+  </si>
+  <si>
+    <t>24.83 ± 23.68</t>
+  </si>
+  <si>
+    <t>53.34 ± 29.33</t>
+  </si>
+  <si>
+    <t>39.69 ± 26.08</t>
+  </si>
+  <si>
+    <t>36.94 ± 11.15</t>
   </si>
 </sst>
 </file>
@@ -252,6 +556,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -596,14 +901,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.88671875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -622,120 +928,290 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6" t="s">
-        <v>40</v>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9" t="s">
+        <v>62</v>
+      </c>
+      <c r="H9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H10" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" t="s">
+        <v>77</v>
+      </c>
+      <c r="G11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F12" t="s">
+        <v>84</v>
+      </c>
+      <c r="G12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D13" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F13" t="s">
+        <v>91</v>
+      </c>
+      <c r="G13" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -745,15 +1221,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -772,120 +1247,293 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F3" t="s">
+        <v>104</v>
+      </c>
+      <c r="G3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F5" t="s">
+        <v>116</v>
+      </c>
+      <c r="G5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D6" t="s">
+        <v>120</v>
+      </c>
+      <c r="E6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F6" t="s">
+        <v>122</v>
+      </c>
+      <c r="G6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="B7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C7" t="s">
+        <v>125</v>
+      </c>
+      <c r="D7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E7" t="s">
+        <v>127</v>
+      </c>
+      <c r="F7" t="s">
+        <v>128</v>
+      </c>
+      <c r="G7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="B8" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D8" t="s">
+        <v>132</v>
+      </c>
+      <c r="E8" t="s">
+        <v>133</v>
+      </c>
+      <c r="F8" t="s">
+        <v>134</v>
+      </c>
+      <c r="G8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F4" t="s">
-        <v>57</v>
-      </c>
-      <c r="G4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F5" t="s">
-        <v>63</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="B9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C9" t="s">
+        <v>137</v>
+      </c>
+      <c r="D9" t="s">
+        <v>138</v>
+      </c>
+      <c r="E9" t="s">
+        <v>139</v>
+      </c>
+      <c r="F9" t="s">
+        <v>140</v>
+      </c>
+      <c r="G9" t="s">
+        <v>141</v>
+      </c>
+      <c r="H9" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6" t="s">
-        <v>67</v>
-      </c>
-      <c r="E6" t="s">
-        <v>68</v>
-      </c>
-      <c r="F6" t="s">
-        <v>69</v>
-      </c>
-      <c r="G6" t="s">
-        <v>70</v>
+      <c r="B10" t="s">
+        <v>143</v>
+      </c>
+      <c r="C10" t="s">
+        <v>144</v>
+      </c>
+      <c r="D10" t="s">
+        <v>145</v>
+      </c>
+      <c r="E10" t="s">
+        <v>146</v>
+      </c>
+      <c r="F10" t="s">
+        <v>147</v>
+      </c>
+      <c r="G10" t="s">
+        <v>148</v>
+      </c>
+      <c r="H10" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" t="s">
+        <v>150</v>
+      </c>
+      <c r="C11" t="s">
+        <v>151</v>
+      </c>
+      <c r="D11" t="s">
+        <v>152</v>
+      </c>
+      <c r="E11" t="s">
+        <v>153</v>
+      </c>
+      <c r="F11" t="s">
+        <v>154</v>
+      </c>
+      <c r="G11" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C12" t="s">
+        <v>157</v>
+      </c>
+      <c r="D12" t="s">
+        <v>158</v>
+      </c>
+      <c r="E12" t="s">
+        <v>159</v>
+      </c>
+      <c r="F12" t="s">
+        <v>160</v>
+      </c>
+      <c r="G12" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" t="s">
+        <v>162</v>
+      </c>
+      <c r="C13" t="s">
+        <v>163</v>
+      </c>
+      <c r="D13" t="s">
+        <v>164</v>
+      </c>
+      <c r="E13" t="s">
+        <v>165</v>
+      </c>
+      <c r="F13" t="s">
+        <v>166</v>
+      </c>
+      <c r="G13" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>
